--- a/bgt_2026_volumi.xlsx
+++ b/bgt_2026_volumi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcello_galimberti/Desktop/ADI business consulting/Offerte 2024/Arti Grafiche/OEE_board/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcello_galimberti/Documents/Python Scripts/AGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71FFACF4-F47E-284E-821F-22B13C2EE2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F8A6E30-C926-D345-8342-61F866E7C593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3160" yWindow="2860" windowWidth="27320" windowHeight="13500" xr2:uid="{01056800-71B0-3643-87E7-79CA28AB19C6}"/>
+    <workbookView xWindow="5380" yWindow="3700" windowWidth="28660" windowHeight="15600" xr2:uid="{01056800-71B0-3643-87E7-79CA28AB19C6}"/>
   </bookViews>
   <sheets>
     <sheet name="volumi_bgt" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Gruppo_risorse</t>
   </si>
@@ -144,9 +144,6 @@
     <t>Finestratura</t>
   </si>
   <si>
-    <t>Villavara</t>
-  </si>
-  <si>
     <t>Acco</t>
   </si>
   <si>
@@ -157,6 +154,18 @@
   </si>
   <si>
     <t>Expertfold</t>
+  </si>
+  <si>
+    <t>Villavara_Acco</t>
+  </si>
+  <si>
+    <t>Villavara_Fust</t>
+  </si>
+  <si>
+    <t>Villavara_CTPACK</t>
+  </si>
+  <si>
+    <t>Villavara_Expertfold</t>
   </si>
 </sst>
 </file>
@@ -1306,10 +1315,10 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
       </c>
       <c r="C18" s="3">
         <v>1449788.1942218591</v>
@@ -1350,10 +1359,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3">
         <v>1449788.1942218591</v>
@@ -1394,10 +1403,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
         <v>2271612</v>
@@ -1438,10 +1447,10 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="3">
         <v>463389</v>
